--- a/Result/profitability/3078.xlsx
+++ b/Result/profitability/3078.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2175</v>
+        <v>1.1225</v>
       </c>
       <c r="N2" t="n">
-        <v>23.13375</v>
+        <v>22.325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12375</v>
+        <v>0.97</v>
       </c>
       <c r="N3" t="n">
-        <v>21.445</v>
+        <v>20.66375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.97625</v>
+        <v>0.7825</v>
       </c>
       <c r="N4" t="n">
-        <v>19.79875</v>
+        <v>18.825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.745</v>
+        <v>0.57875</v>
       </c>
       <c r="N5" t="n">
-        <v>18.13125</v>
+        <v>16.8875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5750000000000001</v>
+        <v>0.42625</v>
       </c>
       <c r="N6" t="n">
-        <v>16.45375</v>
+        <v>15.5125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4525</v>
+        <v>0.35375</v>
       </c>
       <c r="N7" t="n">
-        <v>16.03875</v>
+        <v>15.23375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.395</v>
+        <v>0.3425</v>
       </c>
       <c r="N8" t="n">
-        <v>15.455</v>
+        <v>15.07875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3078</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1513</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1248</v>
+      </c>
+      <c r="E75" t="n">
+        <v>266</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>77</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>94</v>
+      </c>
+      <c r="K75" t="n">
+        <v>68</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.20875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5833333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.009999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1464007782101167</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8159509202453987</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3618181818181818</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
